--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>46041</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44823</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45328</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45756</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45730</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45730</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46105</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45610</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45559</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45041</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45166</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>45425</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44467</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>44490</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>44592</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>44512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>44535</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45763</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>45359</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45951</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>45342</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>45638</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>46261</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>45478</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46274</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>46241</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>44643</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>46280</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>44530</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44819</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44810</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>45373</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45106</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>45378</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>45547</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>44798</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>45446</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>45971</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>44853</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45996</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>45043</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>44459</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45187</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>45670</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>46241</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>45573</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>44959</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>45210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>45198</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>46269</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>44768</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>44805</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>44810</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>44512</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>44597</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>44461</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>44613</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>44515</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>44511</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>44798</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>44615</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>44497</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>44477</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>44586</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44511</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>44613</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>44615</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44593</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>44523</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>44824</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44504</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>44609</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>44487</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44525</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44606</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44867</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44692</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44734</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>44615</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44488</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44859</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44833</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44859</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>44739</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44735</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44515</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>44461</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44854</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44728</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44635</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44538</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44461</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>44606</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44735</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>44592</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>44462</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>44469</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>44477</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>44648</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>44706</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>44706</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44487</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>44804</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44855</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>44656</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45740</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>45338</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44743</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>45400</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>44783</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44938</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45218</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>44569</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44783</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>44991</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45530</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>44985</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>44901</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>44783</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>44958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45103</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>45113</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45384</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45012</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>44606</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44600</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>44687</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45608</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45771</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>45518</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>45632</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>45272</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45135</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>44735</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45247</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>45089</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>44754</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>44970</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>45259</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45166</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45629</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45110</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45216</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45231</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44972</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45596</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>45546</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45169</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45574</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45708</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>44504</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>45337</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45229</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45264</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45196</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>45040</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>44839</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>45385</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>45460</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>44901</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>45463</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>45544</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>45245</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>45345</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>45078</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>45338</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>45338</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45673</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45673</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>45632</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>45462</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>44948</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>45642</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45015</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45000</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45532</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>45043</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16014,7 +16014,7 @@
         <v>45005</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>44743</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>44743</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>44749</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>44820</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45337</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>45015</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44911</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45128</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>45079</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44523</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45447</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45055</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45678</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45362</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>44601</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>45336</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45105</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45114</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45259</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>44838</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45664</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45517</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>45673</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45359</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>45173</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>45744</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>45874</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>45596</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>45385</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>44935</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>45462</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
         <v>45095</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>45264</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45563</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45187</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>45163</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>45106</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>45436</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>45946</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>46058</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45827</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45390</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>44480</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>46139</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45217</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45818</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45086</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45009</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>45884</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>44670</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45909</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45635</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45804</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>44620</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>45901</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45666</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45856</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45858</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>46136</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45895</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45904</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45904</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45538</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45342</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45166</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45548</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45670</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45407</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45840</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45915</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45359</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45917</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45916</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45917</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45105</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45267</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45159</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45860</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45926</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>44816</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45926</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>45929</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>46142</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45929</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>45532</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45166</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>45217</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45933</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>45336</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44805</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45936</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45482</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45349</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44966</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>44935</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>45890</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45512</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45356</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45426</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44881</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45359</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>45608</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>44973</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45075</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45407</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>44978</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45418</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45418</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>45954</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45296</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>44998</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45436</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45740</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>46084</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45418</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>45706</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>44938</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45436</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45965</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45965</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45965</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45965</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45288</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45831</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45198</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45359</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45608</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45414</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45478</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45362</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>45978</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45698</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>45978</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45436</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>45978</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45978</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44635</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26103,7 +26103,7 @@
         <v>45342</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>45979</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>45136</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>45722</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>45986</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45320</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>45986</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45896</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>45989</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>44657</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>44914</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>45128</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26979,7 +26979,7 @@
         <v>45614</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>45854</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>45692</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>45992</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45903</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45959</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>46163</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45992</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>46163</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45996</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>45996</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45635</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>46167</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45338</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45699</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45210</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45217</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45366</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45324</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>45771</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>45771</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>46008</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45267</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44873</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>45608</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>46013</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>45949</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45341</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>46169</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>45135</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>45090</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>46169</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45236</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>45728</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>46170</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>46170</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>46170</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>44805</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>45608</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>45113</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>45254</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>45349</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>45547</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>46175</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>46037</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44893</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>45733</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>46171</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45436</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>46175</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>45182</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>45476</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>46050</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45166</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>46051</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>45155</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>46052</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>44935</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44739</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>46177</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>45155</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45328</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>46058</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>46063</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>45719</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         <v>46177</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31812,7 +31812,7 @@
         <v>45524</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         <v>46064</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>45005</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>45218</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>44991</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>44868</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44601</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>45426</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>45068</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>45247</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32542,7 +32542,7 @@
         <v>46079</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>45614</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>45614</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32761,7 +32761,7 @@
         <v>46084</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32834,7 +32834,7 @@
         <v>46081</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32907,7 +32907,7 @@
         <v>46084</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>45680</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>46084</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33126,7 +33126,7 @@
         <v>46188</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>46186</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>45305</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>46185</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>46087</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45726</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45613</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>46092</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>46094</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>46098</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45114</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>46098</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>46196</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>46195</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>46196</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>44998</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>46106</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>46106</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44943</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45362</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>45644</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44995</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44994</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>45267</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>45076</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>46120</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>45092</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>46244</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>46122</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>46122</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45308</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>46122</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>46122</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>46122</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>45161</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45359</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>46129</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>46129</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>46129</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>46244</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45524</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>46132</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>44880</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44907</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>46132</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36421,7 +36421,7 @@
         <v>45180</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45210</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45385</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45300</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45358</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>45838</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>45988</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>46204</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>46204</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44925</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>45407</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>45189</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>46204</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>45834</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45302</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>45471</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>44951</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>46204</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>45544</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45032</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>46246</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>46203</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45217</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>45128</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>45744</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>44747</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>44978</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>44581</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>45544</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>46206</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>45329</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>46252</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>45136</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45436</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38903,7 +38903,7 @@
         <v>45555</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>45565</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>45595</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>46209</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39195,7 +39195,7 @@
         <v>46212</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>45308</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45146</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>45330</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>44735</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39565,7 +39565,7 @@
         <v>45618</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39638,7 +39638,7 @@
         <v>45608</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         <v>45342</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>46259</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>44895</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39930,7 +39930,7 @@
         <v>45519</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>45763</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>45336</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40149,7 +40149,7 @@
         <v>44545</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45153</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>45153</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>45180</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>44812</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45398</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45149</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45471</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>45471</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45653</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>45447</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45328</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45540</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>45288</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>46269</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44998</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>45712</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45551</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45385</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>46273</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>45113</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45700</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>46272</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>45616</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>46273</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>46273</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>46274</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>45407</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>46274</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>45418</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>46279</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45440</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>46281</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>46281</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45456</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45363</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45705</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>46238</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45790</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45015</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>46241</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>46241</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>46241</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>46241</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>46241</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>45544</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>46241</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>45391</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45418</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45518</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45798</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>44601</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45362</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>45800</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45782</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
         <v>45476</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>44957</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>44816</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>44490</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45811</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>45811</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44602,7 +44602,7 @@
         <v>45811</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45811</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44748,7 +44748,7 @@
         <v>45384</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45824</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45821</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>45825</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45827</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45831</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45769</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>45833</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45833</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>45834</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>45834</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>45838</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45838</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45838</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>45841</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45847</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>45852</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45628</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>45547</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45593</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>44495</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45868</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45467</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45874</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45875</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>44743</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46646,7 +46646,7 @@
         <v>45350</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46719,7 +46719,7 @@
         <v>44903</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46792,7 +46792,7 @@
         <v>44675</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>44675</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46938,7 +46938,7 @@
         <v>45111</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45532</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47084,7 +47084,7 @@
         <v>45481</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>44497</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47230,7 +47230,7 @@
         <v>45532</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>45267</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45435</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>44643</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45709</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         <v>45694</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45720</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>45694</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45701</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>45714</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45694</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>45814</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48106,7 +48106,7 @@
         <v>45972</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48179,7 +48179,7 @@
         <v>45971</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>46040</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>46056</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>46071</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48471,7 +48471,7 @@
         <v>46099</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48544,7 +48544,7 @@
         <v>46191</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48617,7 +48617,7 @@
         <v>46251</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48690,7 +48690,7 @@
         <v>46251</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>46041</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44823</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45328</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45756</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45730</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45730</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46105</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45559</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45610</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45041</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45166</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>45425</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44467</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>44490</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>44592</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>44535</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45359</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>45951</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45638</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>45342</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>45478</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>46261</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>46274</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46241</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>44512</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>44643</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>46280</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>44530</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44819</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45378</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>45573</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>44853</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>44798</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45996</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45971</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45187</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>45547</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>46241</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>44810</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45446</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45043</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45106</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>45373</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45670</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44959</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>45198</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>46269</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>44768</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>44512</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>44597</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44798</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>44615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44477</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44511</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44615</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44613</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>44593</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44523</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44824</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44504</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44609</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44487</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44525</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44606</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44867</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44692</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44734</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>44615</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>44488</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>44859</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44833</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>44859</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>44739</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44515</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>44735</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44854</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>44728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44635</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>44606</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>44592</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>44477</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>44469</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>44648</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44706</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44706</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>44487</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>44804</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>44855</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45329</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45267</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>44743</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44783</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45512</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>45105</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>44739</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>45618</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>45359</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>44893</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>45698</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>45136</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>45128</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45359</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>45217</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>45259</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>45384</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>45236</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>45407</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>44901</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>44901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>44839</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>45462</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44881</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>45320</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>45217</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>45341</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>45949</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44973</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45544</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>45436</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44504</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45342</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45342</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45798</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45015</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45012</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45418</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>45391</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>44490</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45744</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45804</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>45518</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>44873</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>46037</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44957</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>45414</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45305</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45518</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45362</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45436</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45460</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45113</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44656</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45574</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45800</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>45901</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44601</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45904</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>46050</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45904</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>45895</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>45362</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44938</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>46052</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>46051</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>45670</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>46058</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>45349</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>45447</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>45544</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>45548</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>45916</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>45915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>45524</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45390</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>45917</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>46063</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>46064</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45917</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45359</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45359</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45546</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45782</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>44816</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45476</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44838</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45860</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45926</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45565</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45926</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>46079</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>44600</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45929</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>45929</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>44972</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>46081</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>45338</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>46084</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>46084</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>46084</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>45229</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>46087</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45933</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>45936</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>46092</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>46094</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45890</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>46098</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>46098</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>45259</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>45218</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>44783</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45811</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>46106</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>46106</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>45608</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45068</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45954</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45811</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45811</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45712</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44735</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>45811</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45426</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>46120</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>46122</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>46122</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45965</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>46122</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>46122</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>45965</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>45965</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>46122</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>45090</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45965</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45198</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45831</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>45075</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>44991</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45079</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44735</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45359</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>44805</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45978</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>46129</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45978</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>46129</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45978</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45978</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45166</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>46132</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45166</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>46129</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>46132</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45385</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45979</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44747</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45471</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45300</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45614</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45614</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45986</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45135</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45986</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45874</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45856</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>44783</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45884</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>46136</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45163</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45673</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45673</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45189</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>45664</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45989</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45818</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>45635</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>45838</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45666</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45992</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45722</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>45909</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45005</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>45992</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>45946</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>45629</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45385</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44820</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>45740</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>44951</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45996</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         <v>45644</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>46058</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>45113</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>45384</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>45840</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>46139</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>45988</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>45858</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>45476</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45407</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>45763</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>46008</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>46013</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45824</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>45834</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>45092</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>45821</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45267</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45247</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>45827</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45825</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44805</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>45771</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>46142</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45524</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>45532</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>45827</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45247</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45103</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45076</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45538</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44868</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>44749</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45831</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>44880</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45769</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>46084</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>45834</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>45719</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>45128</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45834</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>45337</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>45833</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>45555</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>45078</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>45838</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>45838</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45296</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>45744</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44935</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>45959</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>45726</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>45436</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>45854</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>45436</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44816</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45896</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>45015</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>45110</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>44907</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>45903</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>45114</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>45841</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>46163</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>46163</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>46167</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45847</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45015</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>45852</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>45337</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>46169</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>46169</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29575,7 +29575,7 @@
         <v>46170</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>45519</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>44495</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45547</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45628</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45593</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>46171</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>46170</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>46170</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45547</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>46175</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44966</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>46175</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44925</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45868</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44601</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45463</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>46177</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>45540</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>45467</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31040,7 +31040,7 @@
         <v>46177</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>45482</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45000</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>45563</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>45180</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>45771</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45771</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>45874</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>45632</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>45418</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>45418</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45614</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>46185</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>45642</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>46186</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>45161</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         <v>45342</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45517</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>46188</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45608</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32505,7 +32505,7 @@
         <v>45699</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32578,7 +32578,7 @@
         <v>45613</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45328</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32724,7 +32724,7 @@
         <v>45009</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>44998</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>45632</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>45875</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>45608</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45447</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45210</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>45114</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44569</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44606</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45733</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>46196</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>46196</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45218</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45471</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45471</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>45608</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45338</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45338</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>45345</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45608</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>44523</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>44581</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45608</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>46203</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45182</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45187</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>46204</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>46204</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45366</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>46204</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>46204</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>45680</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>46209</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>45728</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45095</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>46206</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>46252</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45400</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>45653</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>46212</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>45173</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>45155</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>46259</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45398</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>44743</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44743</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>45153</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>45153</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>45231</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>45288</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>45308</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>45149</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>45166</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45135</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45217</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45336</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45349</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>45362</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>45330</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>44670</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>46272</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>46269</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>46273</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45217</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45462</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>46273</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>46274</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>46273</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45264</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>46274</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45272</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45166</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45740</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45136</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45216</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>44895</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45595</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>45338</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>44970</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46279</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45180</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>46281</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>46281</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         <v>46238</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>45302</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39012,7 +39012,7 @@
         <v>44985</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>45532</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>46286</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>46286</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>46286</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>45324</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>46241</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>46241</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>44635</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>46286</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>46241</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>46241</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>46241</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>46241</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>46286</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>46286</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44991</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>44935</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>46288</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>45336</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>45436</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>46244</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>46288</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>46287</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>46244</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44601</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>45426</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>45040</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>44545</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>44938</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>44948</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>44901</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>44657</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45385</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>46290</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>46246</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45356</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>45086</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45436</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>44943</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>45245</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>44935</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>44480</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45155</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>44914</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45678</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>45596</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45005</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45196</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44687</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45146</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>44978</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>45288</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45478</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>44995</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45407</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>45673</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>45706</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>44754</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45210</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>45128</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>45692</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>45159</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>45169</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>44998</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>45089</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45708</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45254</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45336</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45328</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45055</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>45105</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45635</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>45032</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>45596</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45106</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>44620</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>45362</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>44911</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45308</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45544</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>44978</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44994</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>45267</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45530</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>44998</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45264</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45358</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>44958</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>45043</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45587,7 +45587,7 @@
         <v>44812</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45418</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>45551</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45113</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45385</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45616</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45700</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>45407</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>45418</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>45440</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45790</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>45456</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45705</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45363</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>44675</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>44675</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>44643</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46828,7 +46828,7 @@
         <v>44743</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45350</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46974,7 +46974,7 @@
         <v>44903</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47047,7 +47047,7 @@
         <v>45111</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>45532</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>45481</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>44497</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45532</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47412,7 +47412,7 @@
         <v>45267</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45435</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45709</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>45694</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>45720</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45694</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45701</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>45714</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>45694</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48069,7 +48069,7 @@
         <v>45814</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45972</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48215,7 +48215,7 @@
         <v>45971</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48288,7 +48288,7 @@
         <v>46040</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>46056</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>46071</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>46099</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48580,7 +48580,7 @@
         <v>46191</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48653,7 +48653,7 @@
         <v>46251</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>46251</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>46041</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44823</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45328</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45756</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45730</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45730</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46105</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45559</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45610</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45041</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45166</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>45425</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>44467</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>44490</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>44592</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>44535</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45359</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>45951</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45638</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>45342</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>45478</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>46261</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>46274</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46241</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>44512</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>44643</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>46280</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>44530</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44819</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45378</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>45573</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>44853</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>44798</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45996</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45971</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45187</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>45547</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>46241</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>44810</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45446</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45043</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45106</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>45373</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>45670</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44959</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>45198</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>46269</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>44768</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>44512</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>44597</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44798</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>44615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44477</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44511</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44615</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44613</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>44593</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44523</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>44824</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>44504</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44609</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44487</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44525</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>44606</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44867</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44692</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44734</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>44615</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>44488</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>44859</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44833</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>44859</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>44739</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44515</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>44735</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44854</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>44728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44635</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>44606</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>44592</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>44477</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>44469</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>44648</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44706</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44706</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>44487</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>44804</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>44855</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>45329</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45267</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>44743</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44783</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45512</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>45105</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>44739</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>45618</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>45359</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>44893</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>45698</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>45136</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>45128</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45359</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>45217</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>45259</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>45384</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>45236</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>45407</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>44901</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>44901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>44839</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>45462</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44881</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>45320</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>45217</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>45341</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>45949</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44973</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45544</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>45436</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44504</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45342</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45342</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45798</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45015</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45012</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45418</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>45391</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>44490</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45744</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45804</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>45518</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>44873</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>46037</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44957</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>45414</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45305</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45518</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45362</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45436</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45460</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45113</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44656</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45574</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45800</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>45901</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44601</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45904</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>46050</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45904</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>45895</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>45362</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44938</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>46052</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>46051</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>45670</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>46058</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>45349</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>45447</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>45544</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>45548</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>45916</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>45915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>45524</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>45390</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>45917</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>46063</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>46064</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45917</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45359</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45359</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45546</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45782</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>44816</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45476</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44838</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45860</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45926</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45565</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45926</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>46079</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>44600</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45929</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>45929</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>44972</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>46081</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>45338</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>46084</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>46084</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>46084</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>45229</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>46087</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45933</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>45936</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>46092</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>46094</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45890</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>46098</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>46098</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>45259</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>45218</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>44783</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45811</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>46106</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>46106</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>45608</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45068</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45954</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45811</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45811</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45712</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44735</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>45811</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45426</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>46120</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>46122</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>46122</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45965</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>46122</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>46122</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>45965</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>45965</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>46122</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>45090</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45965</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45198</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45831</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>45075</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>44991</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45079</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44735</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45359</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>44805</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45978</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>46129</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45978</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>46129</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45978</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45978</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45166</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>46132</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45166</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>46129</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>46132</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45385</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45979</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44747</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45471</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45300</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45614</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45614</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45986</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45135</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45986</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45874</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45856</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>44783</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45884</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>46136</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45163</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45673</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45673</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45189</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>45664</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45989</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45818</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>45635</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>45838</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45666</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45992</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45722</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>45909</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45005</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>45992</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>45946</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>45629</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45385</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44820</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>45740</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>44951</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45996</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         <v>45644</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>46058</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>45113</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>45384</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>45840</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>46139</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>45988</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>45858</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>45476</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>45407</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>45763</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>46008</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>46013</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45824</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>45834</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>45092</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>45821</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45267</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45247</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>45827</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45825</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44805</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>45771</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>46142</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45524</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>45532</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>45827</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45247</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45103</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45076</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45538</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44868</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>44749</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45831</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>44880</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45769</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>46084</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>45834</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>45719</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>45128</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45834</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>45337</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>45833</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>45555</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>45078</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>45838</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>45838</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45296</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>45744</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44935</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>45959</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>45726</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>45436</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>45854</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>45436</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44816</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45896</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>45015</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>45110</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>44907</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>45903</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>45114</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>45841</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>46163</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>46163</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>46167</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45847</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45015</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>45852</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>45337</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>46169</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>46169</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29575,7 +29575,7 @@
         <v>46170</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>45519</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>44495</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45547</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45628</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45593</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>46171</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>46170</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>46170</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45547</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>46175</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44966</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>46175</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44925</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45868</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>44601</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45463</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>46177</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>45540</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>45467</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31040,7 +31040,7 @@
         <v>46177</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>45482</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45000</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>45563</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>45180</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>45771</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45771</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>45874</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>45632</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>45418</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>45418</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45614</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>46185</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>45642</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>46186</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>45161</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         <v>45342</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45517</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>46188</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45608</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32505,7 +32505,7 @@
         <v>45699</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32578,7 +32578,7 @@
         <v>45613</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45328</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32724,7 +32724,7 @@
         <v>45009</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>44998</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>45632</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>45875</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>45608</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45447</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45210</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>45114</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44569</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>44606</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45733</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>46196</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>46196</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45218</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45471</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45471</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>45608</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45338</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45338</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>45345</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45608</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>44523</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>44581</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45608</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>46203</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45182</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45187</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>46204</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>46204</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45366</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>46204</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>46204</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>45680</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>46209</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>45728</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45095</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>46206</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>46252</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45400</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>45653</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>46212</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>45173</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35795,7 +35795,7 @@
         <v>45155</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>46259</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45398</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>44743</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44743</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>45153</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>45153</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>45231</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>45288</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>45308</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>45149</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>45166</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45135</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45217</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45336</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>45349</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>45362</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>45330</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>44670</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>46272</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>46269</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>46273</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45217</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45462</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>46273</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>46274</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>46273</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45264</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>46274</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45272</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45166</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45740</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45136</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45216</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>44895</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45595</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>45338</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>44970</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>46279</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45180</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>46281</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>46281</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         <v>46238</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>45302</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39012,7 +39012,7 @@
         <v>44985</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>45532</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>46286</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>46286</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>46286</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>45324</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>46241</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>46241</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>44635</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>46286</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>46241</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>46241</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>46241</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>46241</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>46286</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>46286</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44991</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>44935</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>46288</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>45336</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>45436</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>46244</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>46288</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>46287</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>46244</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44601</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>45426</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>45040</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>44545</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>44938</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>44948</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>44901</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>44657</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45385</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>46290</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>46246</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45356</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>45086</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45436</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>44943</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>45245</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>44935</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>44480</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45155</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>44914</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45678</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>45596</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45005</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45196</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44687</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45146</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>44978</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>45288</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45478</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>44995</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45407</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>45673</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>45706</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>44754</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45210</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>45128</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>45692</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>45159</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>45169</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>44998</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>45089</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45708</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45254</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45336</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45328</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45055</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>45105</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45635</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>45032</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>45596</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45106</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>44620</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>45362</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>44911</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45308</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45544</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44925,7 +44925,7 @@
         <v>44978</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44994</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>45267</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45530</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>44998</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45264</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45358</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>44958</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>45043</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45587,7 +45587,7 @@
         <v>44812</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45418</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>45551</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45113</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45385</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45616</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45700</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>45407</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>45418</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>45440</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45790</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>45456</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45705</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45363</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>44675</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>44675</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>44643</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46828,7 +46828,7 @@
         <v>44743</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45350</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46974,7 +46974,7 @@
         <v>44903</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47047,7 +47047,7 @@
         <v>45111</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>45532</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>45481</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>44497</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45532</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47412,7 +47412,7 @@
         <v>45267</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45435</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45709</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>45694</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>45720</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45694</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45701</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>45714</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>45694</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48069,7 +48069,7 @@
         <v>45814</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45972</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48215,7 +48215,7 @@
         <v>45971</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48288,7 +48288,7 @@
         <v>46040</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>46056</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>46071</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>46099</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48580,7 +48580,7 @@
         <v>46191</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48653,7 +48653,7 @@
         <v>46251</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>46251</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>46041</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44823</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45328</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45756</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45730</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45730</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46105</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45559</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45610</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45041</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45166</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>46297</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45425</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44490</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44592</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45670</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44535</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45951</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>45359</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>45342</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>46261</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>46274</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>46241</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>45638</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>45478</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>46280</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44819</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45573</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45373</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>45106</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45378</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45547</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45996</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44798</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>45446</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44853</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>45971</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>45112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>46241</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>45043</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45187</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44959</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>45210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45198</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>46269</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44768</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44512</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44597</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44798</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44477</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44511</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44613</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44615</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44593</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44523</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44824</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44504</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44609</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44487</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44525</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44606</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44867</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44692</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44734</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44615</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>44488</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44859</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>44833</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44859</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>44739</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44515</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>44735</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44854</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44635</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44606</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44592</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44477</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44648</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44706</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44706</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44804</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>44855</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>45740</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>45338</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>45400</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44783</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44743</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>45218</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>44938</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44783</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>44991</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45530</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44569</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>44783</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>45384</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>45012</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>44600</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>44958</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44985</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>45608</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>45103</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>44901</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>45113</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44606</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44687</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>45440</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>45804</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>45771</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>45518</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45632</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>44754</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>45456</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>45363</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>46013</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45272</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>45187</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45135</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44735</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>45247</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>45949</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>45341</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45705</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45089</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44970</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45259</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45629</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>45166</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45790</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45216</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45901</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>45110</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>46037</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45895</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>45904</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45904</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45231</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>44972</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45670</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>45574</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>45596</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>45546</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45169</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>45015</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45544</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44504</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>45915</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45708</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45917</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45391</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>45337</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>45418</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45518</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>45916</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45917</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45798</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44601</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45362</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>46050</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45800</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>45782</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45476</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>44957</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>44816</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44490</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>46051</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45229</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45264</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45811</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>46052</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>45860</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45196</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45040</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44839</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>45385</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>45926</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45926</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>45929</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>45460</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45929</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>46058</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>46063</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>45463</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>45933</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>46064</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>45544</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>45245</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45936</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44901</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>44901</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45811</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45890</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>45811</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45338</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>45338</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45345</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>45078</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>45462</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45632</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45642</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45673</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>45673</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44948</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>45811</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>45015</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>46079</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>45532</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>46084</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>46081</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>45000</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>46084</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45043</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>46084</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45954</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>46087</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45005</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>46092</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45965</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45965</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45965</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45965</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>44743</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>44743</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>44749</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>44820</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>46094</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>45831</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>45337</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45015</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>46098</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>46098</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45359</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>45173</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>44911</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>45055</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45128</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45978</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45447</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44601</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>46106</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>45978</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>45105</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>46106</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45978</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45978</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45079</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44523</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45678</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45384</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45362</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45979</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45336</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45664</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>45517</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45114</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45259</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>44838</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45986</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>45986</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45824</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45821</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>45989</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45673</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>45825</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46120</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45596</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>46122</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45992</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>44935</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>46122</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>46122</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>46122</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>46122</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45462</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45359</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>45095</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>45264</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>46129</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45563</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>46129</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>46129</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45996</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45163</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45827</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>45106</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45436</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>46132</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>46132</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>45831</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45769</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>45833</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>45390</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44480</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>45300</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>45834</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>45838</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>45086</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45834</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45009</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>44670</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>45988</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45838</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45838</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45407</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45189</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45841</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>45635</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>45834</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>44620</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>45471</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>44951</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45874</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45385</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>45847</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45538</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45342</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45166</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45548</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45407</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45946</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45852</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>46058</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>45827</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45359</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>46139</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45105</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>45818</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45884</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45909</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45267</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45159</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>45666</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45856</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45858</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>46136</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>44816</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45628</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>45532</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>45547</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>45593</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>45166</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44495</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45217</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45336</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>44805</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>45482</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45349</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>45840</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>44966</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44935</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>45512</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>45868</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45467</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45356</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45426</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>44881</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45359</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45608</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>46142</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44973</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45075</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>45407</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44978</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45418</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45418</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45296</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>44998</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45436</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45740</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45418</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45706</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>44938</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>46084</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45436</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45288</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45198</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45359</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45896</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45854</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45874</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>45903</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45875</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45959</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>45608</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>46163</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45414</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45478</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45362</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>45698</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>46163</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45436</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>44635</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>46167</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45342</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45136</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45722</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>46169</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>46169</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>46170</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>46170</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>46170</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45320</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>44657</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45547</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>44914</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>45128</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>45614</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>46175</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>45692</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>46171</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>46175</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45744</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45217</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>46177</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45635</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>46188</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>46186</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45338</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45699</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45210</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45217</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45366</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>46185</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45324</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>45771</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>45771</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>45267</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>46196</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>44873</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>45608</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>46196</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>45135</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45090</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45236</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>45728</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44805</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>45608</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45113</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>46204</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>46204</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>46204</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>46204</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45254</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>46203</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>45349</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>44893</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>46206</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45733</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>46209</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>46212</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>46259</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45436</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45182</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>45476</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>45166</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45155</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>44935</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44739</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45155</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>45328</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>45719</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>45524</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>45005</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45218</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>44991</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38211,7 +38211,7 @@
         <v>44868</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38284,7 +38284,7 @@
         <v>46269</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>44601</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>46273</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>45426</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>46272</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>46273</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>45068</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>45247</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>46273</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45614</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39014,7 +39014,7 @@
         <v>45614</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>45680</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         <v>46274</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>46274</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>46279</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>45305</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>46281</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>46281</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>46238</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39671,7 +39671,7 @@
         <v>45726</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45613</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         <v>45114</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>46286</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>44998</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>46286</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40109,7 +40109,7 @@
         <v>46286</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>46286</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>46286</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>44943</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>45362</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>46286</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>45644</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>46244</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>46241</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>46241</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>46241</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>46241</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>46287</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>46241</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>46241</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>46244</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>44995</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>46288</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>46246</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>44994</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45267</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41642,7 +41642,7 @@
         <v>45076</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>46288</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41788,7 +41788,7 @@
         <v>45092</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45308</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45161</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>46290</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45524</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>44880</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>44907</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
         <v>46293</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>45180</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>45210</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>46293</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>45385</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>45358</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>46252</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>44925</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45302</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45544</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>45032</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45217</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>45128</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>46297</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43326,7 +43326,7 @@
         <v>45744</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>44747</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>44978</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>46296</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43618,7 +43618,7 @@
         <v>44581</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45544</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>45329</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43837,7 +43837,7 @@
         <v>45136</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>45436</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>45555</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>45565</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44129,7 +44129,7 @@
         <v>45595</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45308</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45146</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>45330</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>44735</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45618</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45608</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45342</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>44895</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45519</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45763</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45336</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>44545</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45153</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>45153</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45180</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45302,7 +45302,7 @@
         <v>44812</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45398</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45149</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45471</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45594,7 +45594,7 @@
         <v>45471</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45653</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45447</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45328</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45540</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>45288</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46032,7 +46032,7 @@
         <v>44998</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>45712</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45551</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45385</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45113</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45700</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45616</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46543,7 +46543,7 @@
         <v>45407</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45418</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>44743</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>45350</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         <v>44903</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>44675</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>44675</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45111</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45532</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47200,7 +47200,7 @@
         <v>45481</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>44497</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45532</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47419,7 +47419,7 @@
         <v>45267</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>45435</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47565,7 +47565,7 @@
         <v>44643</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47638,7 +47638,7 @@
         <v>45709</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47711,7 +47711,7 @@
         <v>45694</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45720</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45694</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>45701</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45714</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45694</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45814</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>45972</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>45971</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48368,7 +48368,7 @@
         <v>46040</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>46056</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48514,7 +48514,7 @@
         <v>46071</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48587,7 +48587,7 @@
         <v>46099</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48660,7 +48660,7 @@
         <v>46191</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48733,7 +48733,7 @@
         <v>46251</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>46296</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48879,7 +48879,7 @@
         <v>46251</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>46041</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44823</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45328</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45756</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45730</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45730</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46105</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45559</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45610</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45041</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45166</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>46297</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45425</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44490</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44592</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45670</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44535</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45951</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>45359</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>45342</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>46261</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>46274</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>46241</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>45638</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>45478</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>46280</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44819</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45573</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45373</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>45106</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45378</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45547</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45996</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44798</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>45446</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44853</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>45971</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>45112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>46241</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>45043</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45187</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44959</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>45210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45198</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>46269</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44768</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44512</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44597</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44798</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44477</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44511</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44613</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44615</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44593</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44523</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44824</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44504</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44609</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44487</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44525</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44606</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44867</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44692</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44734</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44615</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>44488</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44859</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>44833</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44859</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>44739</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44515</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>44735</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44854</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44635</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44606</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44592</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44477</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44648</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44706</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44706</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44804</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>44855</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>45740</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>45338</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>44656</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>45400</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44783</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44743</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>45218</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>44938</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44783</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>44991</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45530</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44569</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>44783</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>45384</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>45012</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>44600</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>44958</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44985</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>45608</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>45103</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>44901</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>45113</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44606</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44687</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>45440</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>45804</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>45771</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>45518</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45632</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>44754</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>45456</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>45363</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>46013</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45272</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>45187</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45135</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44735</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>45247</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>45949</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>45341</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45705</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45089</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44970</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45259</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45629</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>45166</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45790</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45216</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45901</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>45110</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>46037</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45895</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>45904</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45904</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45231</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>44972</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45670</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>45574</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>45596</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>45546</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45169</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>45015</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45544</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44504</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>45915</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45708</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45917</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45391</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>45337</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>45418</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45518</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>45916</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45917</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45798</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>44601</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45362</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>46050</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45800</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>45782</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45476</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>44957</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>44816</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44490</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>46051</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45229</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45264</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45811</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>46052</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>45860</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45196</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45040</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44839</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>45385</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>45926</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45926</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>45929</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>45460</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45929</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>46058</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>46063</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>45463</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>45933</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>46064</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>45544</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>45245</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45936</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44901</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>44901</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45811</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45890</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>45811</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45338</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>45338</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45345</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>45078</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>45462</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45632</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45642</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45673</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>45673</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44948</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>45811</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>45015</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>46079</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>45532</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>46084</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>46081</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>45000</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>46084</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45043</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>46084</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45954</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>46087</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45005</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>46092</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45965</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45965</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45965</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45965</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>44743</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>44743</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>44749</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>44820</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>46094</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>45831</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>45337</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45015</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>46098</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>46098</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45359</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>45173</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>44911</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>45055</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45128</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45978</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45447</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44601</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>46106</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>45978</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>45105</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>46106</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45978</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45978</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45079</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44523</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45678</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45384</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45362</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45979</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45336</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45664</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>45517</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45114</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45259</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>44838</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45986</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>45986</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45824</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45821</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>45989</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45673</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>45825</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46120</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45596</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>46122</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45992</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>44935</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>46122</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>46122</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>46122</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>46122</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45462</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45359</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>45095</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>45264</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>46129</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45563</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>46129</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>46129</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45996</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45163</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45827</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>45106</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45436</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>46132</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>46132</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>45831</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45769</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>45833</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>45390</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44480</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>45300</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>45834</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>45838</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>45086</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45834</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45009</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>44670</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>45988</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45838</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45838</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45407</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45189</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45841</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>45635</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>45834</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>44620</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>45471</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>44951</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45874</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45385</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>45847</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45538</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45342</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45166</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45548</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45407</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45946</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45852</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>46058</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>45827</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45359</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>46139</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45105</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>45818</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45884</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45909</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45267</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45159</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>45666</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45856</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45858</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>46136</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>44816</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45628</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>45532</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>45547</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>45593</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>45166</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44495</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45217</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45336</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>44805</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>45482</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45349</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>45840</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>44966</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44935</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>45512</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>45868</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45467</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45356</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45426</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>44881</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45359</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45608</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>46142</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44973</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45075</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>45407</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44978</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45418</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45418</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45296</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>44998</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45436</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45740</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45418</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45706</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>44938</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>46084</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45436</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45288</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45198</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45359</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45896</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45854</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45874</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>45903</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45875</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45959</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>45608</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>46163</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45414</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45478</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45362</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>45698</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>46163</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45436</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>44635</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>46167</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45342</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45136</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45722</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>46169</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>46169</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>46170</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>46170</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>46170</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45320</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>44657</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45547</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>44914</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>45128</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>45614</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>46175</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>45692</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>46171</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>46175</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45744</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45217</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>46177</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45635</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>46188</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>46186</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45338</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45699</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45210</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45217</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45366</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>46185</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45324</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>45771</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>45771</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>45267</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>46196</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>44873</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>45608</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>46196</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>45135</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45090</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45236</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>45728</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44805</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>45608</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45113</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>46204</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>46204</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>46204</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>46204</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45254</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>46203</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>45349</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>44893</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>46206</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45733</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>46209</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>46212</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>46259</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45436</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45182</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>45476</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>45166</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45155</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>44935</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44739</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45155</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>45328</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>45719</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>45524</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>45005</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45218</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>44991</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38211,7 +38211,7 @@
         <v>44868</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38284,7 +38284,7 @@
         <v>46269</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>44601</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>46273</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>45426</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>46272</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>46273</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>45068</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>45247</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>46273</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45614</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39014,7 +39014,7 @@
         <v>45614</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>45680</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         <v>46274</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>46274</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>46279</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>45305</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>46281</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>46281</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>46238</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39671,7 +39671,7 @@
         <v>45726</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45613</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         <v>45114</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>46286</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>44998</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>46286</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40109,7 +40109,7 @@
         <v>46286</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>46286</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>46286</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>44943</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>45362</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>46286</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>45644</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>46244</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>46241</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>46241</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>46241</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>46241</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>46287</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>46241</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>46241</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>46244</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>44995</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>46288</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>46246</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>44994</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45267</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41642,7 +41642,7 @@
         <v>45076</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>46288</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41788,7 +41788,7 @@
         <v>45092</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45308</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45161</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>46290</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45524</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>44880</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>44907</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
         <v>46293</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>45180</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>45210</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>46293</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>45385</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>45358</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>46252</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>44925</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45302</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45544</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>45032</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45217</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>45128</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>46297</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43326,7 +43326,7 @@
         <v>45744</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>44747</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>44978</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>46296</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43618,7 +43618,7 @@
         <v>44581</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>45544</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>45329</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43837,7 +43837,7 @@
         <v>45136</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>45436</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>45555</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>45565</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44129,7 +44129,7 @@
         <v>45595</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45308</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45146</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44348,7 +44348,7 @@
         <v>45330</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>44735</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45618</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45608</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45342</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>44895</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45519</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45763</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45336</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>44545</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45153</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>45153</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45180</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45302,7 +45302,7 @@
         <v>44812</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45398</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45149</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45471</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45594,7 +45594,7 @@
         <v>45471</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45653</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45447</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45328</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45540</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>45288</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46032,7 +46032,7 @@
         <v>44998</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>45712</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45551</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45385</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45113</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45700</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45616</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46543,7 +46543,7 @@
         <v>45407</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45418</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>44743</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>45350</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         <v>44903</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46908,7 +46908,7 @@
         <v>44675</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>44675</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>45111</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45532</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47200,7 +47200,7 @@
         <v>45481</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47273,7 +47273,7 @@
         <v>44497</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45532</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47419,7 +47419,7 @@
         <v>45267</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>45435</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47565,7 +47565,7 @@
         <v>44643</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47638,7 +47638,7 @@
         <v>45709</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47711,7 +47711,7 @@
         <v>45694</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45720</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45694</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>45701</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45714</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45694</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45814</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>45972</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>45971</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48368,7 +48368,7 @@
         <v>46040</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>46056</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48514,7 +48514,7 @@
         <v>46071</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48587,7 +48587,7 @@
         <v>46099</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48660,7 +48660,7 @@
         <v>46191</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48733,7 +48733,7 @@
         <v>46251</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>46296</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48879,7 +48879,7 @@
         <v>46251</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>46041</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44823</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45328</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45756</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45730</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45730</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46105</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45610</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45559</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45041</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45166</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>46297</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45425</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44592</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45342</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>44535</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>45359</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45670</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45478</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>45638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45951</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>44512</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45763</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>46241</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>46261</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>46274</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>46280</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44819</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45378</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45573</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>44853</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>45187</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44798</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>45547</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45996</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>44810</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>45446</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45043</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>45106</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>45971</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>45373</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>46241</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44959</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>45210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45198</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>46269</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44768</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44512</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44597</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44798</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44586</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44511</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44613</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44615</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44593</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44523</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44504</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44609</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44487</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44488</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44525</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44859</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44854</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44606</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44728</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44735</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44606</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44635</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>44833</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44867</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>44538</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44592</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>44859</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44734</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44692</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44739</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44615</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44515</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44648</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44706</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44706</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44487</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>45673</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>45706</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44754</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>45210</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44893</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>44804</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>44855</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>45698</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>45136</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45128</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>44749</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45128</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44880</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45719</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45359</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45692</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45128</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>45236</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>45159</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>45337</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>45618</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>45217</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>45259</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>45384</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45555</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45078</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44743</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45329</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>45296</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45744</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>44935</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>45726</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>45267</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>45436</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45436</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44783</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44816</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>45169</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>44998</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>45407</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>44901</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44901</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45015</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>45110</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>45512</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>44907</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>45089</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>45114</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45708</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45105</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>45359</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>45254</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>45336</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44739</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45328</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45187</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45015</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45055</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45337</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45105</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44839</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45635</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45462</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45032</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45217</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44881</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45320</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45596</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45106</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44620</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45362</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>44911</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>45308</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44973</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45544</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>45436</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>45519</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>44978</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>44994</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>45744</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>44504</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45267</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45342</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45804</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45342</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45530</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45544</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>44966</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>44998</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45264</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>44925</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45012</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45358</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44958</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45901</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>44873</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>44601</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>45463</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45414</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45904</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45540</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45904</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45305</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45895</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45482</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45043</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45518</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>45000</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>44812</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45436</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45418</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45460</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45551</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45113</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44656</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45670</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45113</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45574</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45385</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45563</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45180</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45771</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45771</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45632</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45418</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45418</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45362</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44938</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45616</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45700</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45916</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45614</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45915</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45642</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45917</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45161</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>45342</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>45349</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45407</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45917</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45447</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45544</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45517</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45548</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45524</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45390</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45418</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45608</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45359</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45359</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45546</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45699</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45613</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45328</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45440</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45790</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45860</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>45009</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45456</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45926</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44838</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>44998</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45632</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>45608</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45705</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45926</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45447</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45210</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45363</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45565</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45114</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44569</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44606</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45733</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45929</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>45929</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>44600</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44972</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45544</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45218</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>45338</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45471</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>45471</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>45608</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>45338</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45338</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>45345</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>45229</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45798</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45608</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44523</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44581</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45015</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45608</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45418</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45391</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>44490</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45518</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45182</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>44957</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45362</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45800</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>44601</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45933</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45936</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45366</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45782</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44816</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45476</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45680</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45259</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45218</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45728</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45095</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44783</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45400</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45890</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45811</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45811</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45811</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45811</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45608</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45068</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45712</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44735</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45653</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45384</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45426</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45173</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45824</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45155</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45821</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45825</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45090</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45198</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45827</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45075</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>44991</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45079</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45398</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>44743</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>44743</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>44735</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45153</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45153</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45954</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45831</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45769</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45834</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>45834</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>45833</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44805</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>45838</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45231</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45838</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45166</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45965</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45166</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45965</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45965</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45385</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45288</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44747</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45308</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>45831</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>45149</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45614</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>45614</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45135</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>45166</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44783</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45841</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45135</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45163</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45673</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45673</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>45664</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45635</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>45722</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45005</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45847</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45629</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45852</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44820</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45740</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45217</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>45644</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45978</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>44495</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45547</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45628</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>45113</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45336</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>45593</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45349</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>45362</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>45978</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45868</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45467</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45978</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45978</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45330</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>44670</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45476</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45874</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45763</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45217</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45462</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45979</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45875</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45264</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45092</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45272</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45267</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45247</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45166</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>46098</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45740</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>46098</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45136</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>45216</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>44895</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>45595</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45338</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>45986</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>44970</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44805</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45180</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45986</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45771</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45524</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45302</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>44985</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45532</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45247</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45103</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45532</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>45992</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45992</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45324</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44635</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>45076</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45538</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>44868</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>46120</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>44991</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>44935</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>46122</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>46122</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45996</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>46122</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>46122</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>45359</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45336</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>46129</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>46129</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>45436</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>46132</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>46129</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>46132</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45471</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45300</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>44601</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45874</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45426</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45856</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45884</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>45040</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>46136</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>44545</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44938</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>44948</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45189</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>44901</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45818</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>45838</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>45666</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45909</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>44657</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>45385</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37612,7 +37612,7 @@
         <v>45946</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>45385</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>46013</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>44951</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45341</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45949</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45356</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45086</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45436</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>46058</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>44943</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45245</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>45840</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>46139</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45988</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45858</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>45407</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>44935</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>44480</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45155</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>44914</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45678</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45596</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>46037</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>45005</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>45196</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>44687</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>45834</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39656,7 +39656,7 @@
         <v>45146</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>44978</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>45288</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>45478</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>45827</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>46050</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>44995</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>45407</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>46142</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>46052</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>46051</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>46058</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>46063</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40610,7 +40610,7 @@
         <v>46064</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>46084</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>46079</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>46081</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>46084</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>46084</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>46087</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45959</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>45854</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>45896</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>46094</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45903</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>46163</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>46163</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>46167</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>46169</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>46169</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>46170</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>46171</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>46170</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>46170</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>45547</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>46175</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>46175</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>46177</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>46185</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>46186</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>46188</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>46196</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>46196</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>46203</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>46204</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>46204</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>46204</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>46204</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43170,7 +43170,7 @@
         <v>46209</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>46206</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>46212</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>46272</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>46269</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>46273</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>46273</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46274</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>46273</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>46274</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>46279</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>46281</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>46281</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>46238</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>46286</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>46286</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>46286</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>46241</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>46241</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>46286</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>46241</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>46241</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>46241</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
         <v>46241</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>46286</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>46286</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>46288</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45141,7 +45141,7 @@
         <v>46244</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45214,7 +45214,7 @@
         <v>46288</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>46287</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>46244</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>46290</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>46246</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>46293</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>46293</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>46296</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>46252</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>46297</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45949,7 +45949,7 @@
         <v>45989</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>46300</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>46302</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>46259</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>46303</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>46303</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>46304</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>46303</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>46303</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>46092</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>44675</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         <v>44675</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>44643</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>44743</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>45350</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>44903</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45111</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>45532</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45481</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>44497</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47409,7 +47409,7 @@
         <v>45532</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47482,7 +47482,7 @@
         <v>45267</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45435</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45709</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45694</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>45720</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45694</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>45701</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47993,7 +47993,7 @@
         <v>45714</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45694</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>45814</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>45972</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48285,7 +48285,7 @@
         <v>45971</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48358,7 +48358,7 @@
         <v>46040</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>46056</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>46071</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48577,7 +48577,7 @@
         <v>46099</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>46191</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48723,7 +48723,7 @@
         <v>46251</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>46296</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>46296</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>46251</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>46304</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>46304</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>46041</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44823</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45328</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45756</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45730</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45730</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46105</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45610</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45559</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45041</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45166</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>46297</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45425</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44592</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45342</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>44535</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>45359</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>45670</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45478</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>45638</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45951</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>44512</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45763</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>46241</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>46261</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>46274</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>46280</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44819</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45378</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45573</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>44853</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>45187</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44798</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>45547</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45996</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>44810</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>45446</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45043</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>45106</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>45971</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>45373</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>46241</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44959</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>45210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>45198</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>46269</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44768</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44512</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44597</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44798</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44586</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44511</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44613</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44615</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44593</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44523</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44504</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44609</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44487</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44488</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44525</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44859</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44854</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44606</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44728</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44735</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44606</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44635</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>44833</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44867</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>44538</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44592</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>44859</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44734</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44692</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44739</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44615</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44515</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44648</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44706</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44706</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44487</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>45673</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>45706</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44754</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>45210</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44893</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>44804</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>44855</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>45698</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>45136</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45128</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>44749</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45128</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44880</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45719</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45359</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45692</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45128</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>45236</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>45159</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>45337</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>45618</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>45217</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>45259</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>45384</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45555</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45078</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44743</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45329</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>45296</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45744</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>44935</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>45726</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>45267</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>45436</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45436</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44783</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44816</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>45169</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>44998</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>45407</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>44901</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44901</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45015</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>45110</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>45512</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>44907</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>45089</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>45114</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45708</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45105</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>45359</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>45254</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>45336</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44739</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45328</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45187</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45015</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45055</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45337</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45105</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44839</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45635</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45462</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45032</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45217</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>44881</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45320</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45596</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45106</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44620</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45362</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>44911</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>45308</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44973</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45544</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>45436</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>45519</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>44978</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>44994</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>45744</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>44504</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45267</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45342</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45804</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45342</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45530</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45544</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>44966</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>44998</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45264</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>44925</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45012</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45358</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44958</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45901</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>44873</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>44601</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>45463</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45414</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45904</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45540</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45904</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45305</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45895</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45482</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45043</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45518</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>45000</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>44812</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45436</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45418</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45460</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45551</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45113</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44656</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45670</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45113</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45574</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45385</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45563</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45180</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45771</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45771</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45632</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45418</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45418</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45362</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44938</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45616</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45700</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45916</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45614</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45915</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45642</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45917</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45161</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>45342</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>45349</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45407</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45917</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45447</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45544</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45517</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45548</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45524</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45390</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45418</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45608</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45359</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45359</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45546</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45699</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45613</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45328</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45440</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45790</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45860</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>45009</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45456</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45926</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44838</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>44998</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45632</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>45608</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45705</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45926</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45447</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45210</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45363</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45565</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45114</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44569</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44606</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45733</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45929</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>45929</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>44600</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44972</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45544</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45218</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>45338</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45471</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>45471</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>45608</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>45338</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45338</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>45345</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>45229</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45798</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45608</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44523</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44581</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45015</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45608</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45418</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45391</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>44490</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45518</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45182</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>44957</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45362</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45800</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>44601</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45933</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45936</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45366</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45782</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44816</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45476</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45680</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45259</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45218</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45728</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45095</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44783</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45400</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45890</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45811</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45811</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45811</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45811</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45608</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45068</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45712</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44735</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45653</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45384</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45426</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45173</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45824</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45155</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45821</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45825</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45090</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45198</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45827</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45075</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>44991</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45079</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45398</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>44743</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>44743</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>44735</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45153</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45153</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45954</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45831</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45769</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45834</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>45834</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>45833</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44805</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>45838</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45231</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45838</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45166</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45965</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45166</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45965</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45965</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45385</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45288</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44747</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45308</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>45831</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>45149</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45614</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>45614</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45135</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>45166</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44783</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45841</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45135</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45163</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45673</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45673</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>45664</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45635</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>45722</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45005</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45847</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45629</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45852</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44820</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45740</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45217</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>45644</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45978</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>44495</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45547</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45628</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>45113</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45336</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>45593</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45349</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>45362</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>45978</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45868</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45467</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45978</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45978</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45330</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>44670</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45476</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45874</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45763</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45217</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45462</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45979</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45875</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45264</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45092</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45272</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45267</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45247</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45166</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>46098</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45740</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>46098</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45136</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>45216</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>44895</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>45595</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45338</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>45986</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>44970</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44805</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45180</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45986</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45771</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45524</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45302</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>44985</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45532</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45247</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45103</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45532</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>45992</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45992</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45324</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44635</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>45076</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45538</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>44868</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>46120</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>44991</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>44935</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>46122</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>46122</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45996</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>46122</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>46122</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>45359</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45336</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>46129</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>46129</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>45436</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>46132</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>46129</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>46132</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45471</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45300</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>44601</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45874</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45426</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45856</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>45884</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>45040</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>46136</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>44545</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44938</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>44948</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45189</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>44901</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45818</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>45838</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>45666</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45909</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>44657</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>45385</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37612,7 +37612,7 @@
         <v>45946</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>45385</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>46013</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>44951</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45341</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45949</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45356</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45086</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45436</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>46058</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>44943</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45245</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>45840</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>46139</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45988</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45858</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>45407</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>44935</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>44480</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45155</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>44914</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45678</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45596</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>46037</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>45005</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>45196</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>44687</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>45834</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39656,7 +39656,7 @@
         <v>45146</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>44978</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>45288</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>45478</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>45827</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>46050</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>44995</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>45407</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>46142</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>46052</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40386,7 +40386,7 @@
         <v>46051</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>46058</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>46063</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40610,7 +40610,7 @@
         <v>46064</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>46084</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>46079</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>46081</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>46084</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>46084</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>46087</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45959</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>45854</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>45896</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>46094</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45903</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>46163</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>46163</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>46167</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>46169</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>46169</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>46170</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>46171</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>46170</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>46170</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>45547</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>46175</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>46175</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>46177</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>46185</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>46186</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>46188</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>46196</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>46196</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>46203</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>46204</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>46204</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>46204</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>46204</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43170,7 +43170,7 @@
         <v>46209</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>46206</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>46212</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>46272</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>46269</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>46273</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>46273</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46274</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>46273</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>46274</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>46279</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>46281</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>46281</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>46238</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>46286</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>46286</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>46286</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>46241</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>46241</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>46286</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>46241</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>46241</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>46241</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
         <v>46241</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>46286</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>46286</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>46288</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45141,7 +45141,7 @@
         <v>46244</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45214,7 +45214,7 @@
         <v>46288</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>46287</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>46244</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>46290</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>46246</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>46293</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>46293</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>46296</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>46252</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>46297</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45949,7 +45949,7 @@
         <v>45989</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>46300</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>46302</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>46259</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>46303</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>46303</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>46304</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>46303</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>46303</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>46092</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>44675</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         <v>44675</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>44643</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>44743</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>45350</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>44903</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45111</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>45532</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45481</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>44497</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47409,7 +47409,7 @@
         <v>45532</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47482,7 +47482,7 @@
         <v>45267</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45435</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45709</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45694</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>45720</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45694</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>45701</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47993,7 +47993,7 @@
         <v>45714</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45694</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>45814</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>45972</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48285,7 +48285,7 @@
         <v>45971</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48358,7 +48358,7 @@
         <v>46040</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>46056</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>46071</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48577,7 +48577,7 @@
         <v>46099</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>46191</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48723,7 +48723,7 @@
         <v>46251</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>46296</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>46296</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>46251</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>46304</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>46304</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>46041</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44823</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45328</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45756</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45730</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45730</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46105</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45610</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45559</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45041</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45166</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>46297</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>46274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>45425</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44592</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44512</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>44535</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45763</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45951</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45359</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45342</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>46241</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>45638</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45478</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>46261</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>46280</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>44819</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>45373</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45106</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45378</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45547</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44798</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>45971</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>45446</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44853</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>45112</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45996</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>45043</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45187</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>46241</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>45573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>44959</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45198</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>46269</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44768</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>44512</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44597</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44798</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>44615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>44497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44586</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44511</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44613</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44615</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44593</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44523</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>44504</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>44609</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>44487</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>44525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44606</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>44867</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>44734</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44615</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44488</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44859</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>44833</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>44859</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>44739</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>44515</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>44735</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>44854</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>44728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>44538</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>44635</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>44606</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>44735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>44592</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>44648</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>44706</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>44706</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44487</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>44804</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44855</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44656</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>45740</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>45338</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>44743</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45400</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44938</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>44783</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>44991</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44569</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45218</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>45530</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>44985</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>44783</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>44901</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>44958</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>45384</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>45012</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>45103</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>45113</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44600</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>45608</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>45518</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>45632</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>45771</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>44754</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>44606</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>44687</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>45089</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>45272</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>44735</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>45247</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>45135</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>45259</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>45166</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>45216</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>44970</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>45629</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>45110</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>45231</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>45596</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45546</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>45169</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44972</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>45708</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45574</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44504</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>45337</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45229</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>45264</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>45196</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>45040</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>44839</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>45385</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45460</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44901</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44901</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>45544</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45245</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45345</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45078</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>45632</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45338</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45338</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>45642</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45462</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45673</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>45673</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>45000</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>44948</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45043</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>45015</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>45532</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45005</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>44743</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>44743</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44749</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>44820</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45337</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>45015</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>44911</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>45128</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>45359</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>45173</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>45463</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>45447</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>45079</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>44523</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>44601</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45105</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45055</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>45678</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>45362</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>45114</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>45336</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>45259</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>44838</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>45664</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>45517</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45874</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45385</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>45744</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45673</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>45946</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>45596</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>46058</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>45827</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>44935</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>45187</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>46139</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>45462</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45818</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45095</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45264</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45217</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>45884</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45563</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>45163</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45106</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45909</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45436</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>45666</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>45804</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45856</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45858</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>46136</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45390</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45901</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45840</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45086</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45009</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45895</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45904</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44670</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45904</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45670</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>46142</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45635</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45915</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>44620</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>45917</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45916</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45917</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45538</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45342</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45166</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45548</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45407</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45860</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45926</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45359</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45926</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45929</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45929</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45105</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45933</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45936</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>46084</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45890</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45267</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45159</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>44816</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45532</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45166</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45217</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45336</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>44805</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45482</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45349</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>44966</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45954</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44935</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45512</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45896</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45356</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45426</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45854</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>44881</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45965</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45965</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45965</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45359</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45831</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45903</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>45608</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45959</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>44973</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45075</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45407</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>44978</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>46163</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45418</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45418</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45978</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>45978</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>46163</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45978</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45978</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45296</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44998</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45436</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>45740</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>45979</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>45418</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24906,7 +24906,7 @@
         <v>46167</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>45706</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25052,7 +25052,7 @@
         <v>44938</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>45436</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>45288</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>45986</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>45198</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>45986</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>45359</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>45992</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>45992</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>45608</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>46169</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>45414</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45478</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45362</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45698</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>45436</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45996</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44635</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45342</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>46169</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>45136</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>46170</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>46170</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>46170</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>45722</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45547</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45320</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>46175</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44657</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44914</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>45128</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45614</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>46013</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45692</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45949</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45341</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>46171</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46175</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45635</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>45338</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>46037</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>45699</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45210</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>45217</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>45366</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45324</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>46177</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45771</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45771</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45267</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>46050</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>44873</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45608</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>46051</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>46052</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>46058</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>46063</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>45135</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>45090</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>46064</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45236</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45728</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>46188</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>46186</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>44805</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45608</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>45113</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>45254</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>46079</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30099,7 +30099,7 @@
         <v>46185</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>45349</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>46084</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>46081</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>46084</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>44893</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>45733</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>46087</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>46094</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>46098</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>46196</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45436</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>46098</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>45182</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>45476</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
         <v>45166</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45155</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>46196</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31413,7 +31413,7 @@
         <v>44935</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>44739</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>45155</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>45328</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45719</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45524</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>46120</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45005</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>46122</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>46122</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>46122</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>46122</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45218</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>44991</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44868</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45359</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>44601</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>46129</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>46129</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>46129</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45426</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45068</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>46132</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>46132</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45247</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>45614</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>45614</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45300</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45680</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>46204</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>46204</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>46204</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>46204</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45838</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45305</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45988</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>46203</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>45407</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>45189</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45834</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>45471</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44951</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45726</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45613</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>46206</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>45114</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>46209</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>46212</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>44998</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>44943</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45362</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>45644</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44995</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>44994</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45267</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>45076</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>46273</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>45092</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>46272</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>46273</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>45308</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>45161</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>46273</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>46274</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>45524</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>44880</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36231,7 +36231,7 @@
         <v>44907</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>45180</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>46274</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45210</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>45385</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>45358</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36669,7 +36669,7 @@
         <v>46279</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>44925</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>46281</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>46281</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45302</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45544</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45032</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>46238</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45217</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>45128</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>45744</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37472,7 +37472,7 @@
         <v>44747</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>44978</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>46286</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>46286</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>46286</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>46286</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>46286</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>44581</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>45544</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38129,7 +38129,7 @@
         <v>46286</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>45329</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>46244</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45136</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>46241</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>46241</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>46241</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>46241</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>46287</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>45436</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>46241</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>46241</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>46244</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>45555</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45565</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>45595</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>46288</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>45308</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>46246</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>46288</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39589,7 +39589,7 @@
         <v>45146</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>45330</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>44735</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45618</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45608</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>45342</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>46290</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44895</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45519</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45763</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>46293</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45336</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44545</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>46293</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>46252</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>45153</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>45153</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>45180</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>44812</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45398</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>45149</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>45471</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>45471</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>45653</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>45447</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>45328</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>45540</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>46297</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>46296</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>45288</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>44998</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>45712</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>45551</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>45385</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45113</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>45700</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>45989</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>45616</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42373,7 +42373,7 @@
         <v>46300</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45407</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>45418</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>46259</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42665,7 +42665,7 @@
         <v>45440</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42738,7 +42738,7 @@
         <v>46092</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>46302</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>46303</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45456</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45363</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>46303</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>46303</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>46303</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>45705</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>45790</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45015</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>46304</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43614,7 +43614,7 @@
         <v>45544</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>45391</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45418</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45518</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         <v>45798</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>44601</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45362</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45800</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>45782</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44271,7 +44271,7 @@
         <v>45476</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44344,7 +44344,7 @@
         <v>44957</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>44816</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>44490</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44563,7 +44563,7 @@
         <v>46309</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45811</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>45811</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45811</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>45811</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>46269</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
         <v>45384</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>45824</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45821</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>45825</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>45827</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45831</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45769</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45833</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>45834</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45663,7 +45663,7 @@
         <v>45834</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45736,7 +45736,7 @@
         <v>45838</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45809,7 +45809,7 @@
         <v>45838</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
         <v>45841</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45847</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45852</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46101,7 +46101,7 @@
         <v>45628</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45547</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>45593</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>44495</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45868</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45467</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>45874</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45875</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>44743</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45350</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>44903</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>44675</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44675</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45111</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47123,7 +47123,7 @@
         <v>45532</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45481</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>44497</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47342,7 +47342,7 @@
         <v>45532</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45267</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>45435</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>44643</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>45709</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45694</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>45720</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>45694</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47926,7 +47926,7 @@
         <v>45701</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>45714</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48072,7 +48072,7 @@
         <v>45694</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45814</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45972</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48291,7 +48291,7 @@
         <v>45971</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>46040</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48437,7 +48437,7 @@
         <v>46056</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48510,7 +48510,7 @@
         <v>46071</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>46099</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>46191</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48729,7 +48729,7 @@
         <v>46251</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         <v>46296</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>46251</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48948,7 +48948,7 @@
         <v>46296</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>46304</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>46304</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>46041</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44823</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45328</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45756</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45730</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45730</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46105</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45610</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45559</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45041</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45166</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>46297</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>46274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>45425</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44592</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44512</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>44535</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45763</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45951</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45359</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45342</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>46241</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>45638</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45478</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45670</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>46261</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44643</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>46280</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44530</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>44819</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>45373</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>45106</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45378</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45547</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44798</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>45971</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>45446</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44853</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>45112</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45996</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>45043</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45187</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>46241</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>45573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>44959</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45198</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>46269</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44768</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>44512</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44597</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44798</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>44615</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>44497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44586</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44511</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44613</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44615</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44593</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44523</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>44504</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>44609</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>44487</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>44525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44606</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>44867</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>44734</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>44615</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44488</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>44859</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>44833</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>44859</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>44739</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>44515</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>44735</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>44854</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>44728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>44538</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>44635</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>44606</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>44735</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>44592</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>44648</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>44706</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>44706</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44487</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>44804</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44855</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44656</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>45740</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>45338</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>44743</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45400</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44938</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>44783</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>44991</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44569</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45218</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>45530</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>44985</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>44783</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>44901</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>44958</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>45384</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>45012</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>45103</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>45113</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44600</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>45608</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>45518</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>45632</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>45771</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>44754</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>44606</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>44687</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>45089</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>45272</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>44735</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>45247</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>45135</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>45259</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>45166</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>45216</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>44970</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>45629</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>45110</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>45231</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>45596</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45546</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>45169</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44972</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>45708</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45574</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>44504</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>45337</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45229</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>45264</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>45196</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>45040</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>44839</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>45385</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45460</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44901</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44901</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>45544</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45245</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45345</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45078</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>45632</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45338</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45338</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>45642</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45462</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45673</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>45673</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>45000</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>44948</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45043</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>45015</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>45532</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45005</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>44743</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>44743</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44749</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>44820</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45337</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>45015</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>44911</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>45128</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>45359</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>45173</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>45463</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>45447</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>45079</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>44523</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>44601</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45105</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45055</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>45678</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>45362</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>45114</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>45336</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>45259</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>44838</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>45664</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>45517</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45874</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45385</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>45744</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45673</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>45946</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>45596</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>46058</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>45827</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>44935</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>45187</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>46139</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>45462</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45818</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45095</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45264</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45217</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>45884</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45563</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>45163</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45106</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45909</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45436</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>45666</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>45804</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45856</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45858</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>46136</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45390</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45901</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45840</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45086</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45009</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45895</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45904</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>44670</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45904</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45670</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>46142</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45635</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45915</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>44620</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>45917</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45916</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45917</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45538</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45342</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45166</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45548</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45407</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45860</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45926</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45359</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45926</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45929</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45929</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45105</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45933</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45936</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>46084</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45890</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45267</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45159</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>44816</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45532</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45166</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45217</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45336</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>44805</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45482</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45349</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>44966</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45954</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44935</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45512</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45896</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45356</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45426</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45854</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>44881</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>45965</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45965</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45965</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45359</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45831</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45903</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>45608</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45959</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>44973</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45075</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45407</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>44978</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>46163</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45418</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45418</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45978</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>45978</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>46163</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45978</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45978</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45296</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44998</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45436</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>45740</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>45979</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>45418</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24906,7 +24906,7 @@
         <v>46167</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>45706</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25052,7 +25052,7 @@
         <v>44938</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>45436</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>45288</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>45986</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>45198</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>45986</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>45359</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>45992</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>45992</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>45608</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>46169</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>45414</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45478</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45362</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45698</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>45436</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45996</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44635</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45342</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>46169</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>45136</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>46170</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>46170</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>46170</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>45722</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45547</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45320</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>46175</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44657</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44914</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>45128</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45614</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>46013</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45692</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45949</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45341</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>46171</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46175</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45635</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>45338</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>46037</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>45699</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45210</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>45217</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>45366</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45324</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>46177</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45771</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45771</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45267</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>46050</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>44873</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45608</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>46051</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>46052</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>46058</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>46063</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>45135</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>45090</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>46064</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45236</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45728</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>46188</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>46186</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>44805</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45608</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>45113</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>45254</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>46079</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30099,7 +30099,7 @@
         <v>46185</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>45349</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>46084</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>46081</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>46084</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>44893</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>45733</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>46087</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>46094</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>46098</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>46196</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45436</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>46098</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>45182</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>45476</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
         <v>45166</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45155</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>46196</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31413,7 +31413,7 @@
         <v>44935</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>44739</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>45155</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>45328</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45719</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45524</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>46120</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45005</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>46122</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>46122</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>46122</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>46122</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45218</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>44991</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44868</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45359</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>44601</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>46129</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>46129</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>46129</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45426</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45068</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>46132</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>46132</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45247</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>45614</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>45614</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45300</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45680</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>46204</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>46204</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>46204</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>46204</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45838</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45305</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45988</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>46203</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>45407</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>45189</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45834</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>45471</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44951</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45726</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45613</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>46206</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>45114</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>46209</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>46212</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>44998</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>44943</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>45362</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>45644</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44995</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>44994</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45267</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>45076</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>46273</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>45092</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>46272</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>46273</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>45308</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>45161</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35939,7 +35939,7 @@
         <v>46273</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>46274</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>45524</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>44880</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36231,7 +36231,7 @@
         <v>44907</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36304,7 +36304,7 @@
         <v>45180</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>46274</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45210</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36523,7 +36523,7 @@
         <v>45385</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>45358</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36669,7 +36669,7 @@
         <v>46279</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>44925</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>46281</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>46281</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45302</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45544</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45032</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>46238</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45217</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>45128</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>45744</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37472,7 +37472,7 @@
         <v>44747</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>44978</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>46286</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>46286</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>46286</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>46286</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>46286</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>44581</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>45544</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38129,7 +38129,7 @@
         <v>46286</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>45329</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>46244</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45136</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>46241</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>46241</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>46241</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>46241</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>46287</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>45436</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>46241</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>46241</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>46244</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>45555</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45565</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>45595</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>46288</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>45308</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>46246</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>46288</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39589,7 +39589,7 @@
         <v>45146</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>45330</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>44735</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45618</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45608</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>45342</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>46290</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>44895</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45519</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45763</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>46293</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45336</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44545</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>46293</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>46252</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>45153</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>45153</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>45180</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>44812</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45398</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>45149</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>45471</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>45471</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>45653</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>45447</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>45328</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>45540</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>46297</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>46296</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>45288</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>44998</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>45712</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>45551</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>45385</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45113</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>45700</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>45989</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>45616</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42373,7 +42373,7 @@
         <v>46300</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45407</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>45418</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>46259</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42665,7 +42665,7 @@
         <v>45440</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42738,7 +42738,7 @@
         <v>46092</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>46302</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>46303</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45456</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45363</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>46303</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>46303</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>46303</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>45705</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>45790</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45015</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>46304</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43614,7 +43614,7 @@
         <v>45544</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>45391</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45418</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45518</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         <v>45798</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>44601</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45362</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45800</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>45782</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44271,7 +44271,7 @@
         <v>45476</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44344,7 +44344,7 @@
         <v>44957</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>44816</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>44490</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44563,7 +44563,7 @@
         <v>46309</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45811</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>45811</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45811</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>45811</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>46269</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
         <v>45384</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>45824</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45821</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>45825</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>45827</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45831</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45769</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45833</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>45834</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45663,7 +45663,7 @@
         <v>45834</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45736,7 +45736,7 @@
         <v>45838</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45809,7 +45809,7 @@
         <v>45838</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
         <v>45841</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45847</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45852</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46101,7 +46101,7 @@
         <v>45628</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45547</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>45593</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>44495</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45868</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45467</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>45874</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45875</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>44743</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45350</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>44903</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>44675</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44675</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45111</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47123,7 +47123,7 @@
         <v>45532</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45481</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>44497</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47342,7 +47342,7 @@
         <v>45532</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45267</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>45435</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>44643</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>45709</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45694</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>45720</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>45694</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47926,7 +47926,7 @@
         <v>45701</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>45714</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48072,7 +48072,7 @@
         <v>45694</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45814</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45972</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48291,7 +48291,7 @@
         <v>45971</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>46040</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48437,7 +48437,7 @@
         <v>46056</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48510,7 +48510,7 @@
         <v>46071</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>46099</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>46191</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48729,7 +48729,7 @@
         <v>46251</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         <v>46296</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>46251</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48948,7 +48948,7 @@
         <v>46296</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>46304</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>46304</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>46041</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44823</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45328</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45756</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45730</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45730</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46105</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45610</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45559</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45166</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>46297</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>46274</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>45041</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45587</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>45425</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44592</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44535</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45951</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>46241</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>46261</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>45763</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>45359</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>45638</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>45342</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45478</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>44512</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44643</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>46280</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44530</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>44819</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>44810</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>45446</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>45043</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>45106</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45112</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45373</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45378</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45996</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>46241</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>45573</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>45971</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>44853</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44798</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>45187</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45547</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44959</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45210</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45198</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>46269</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>44805</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>44768</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>44805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44810</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>44512</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>44597</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>44613</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44515</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44798</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44511</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44615</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44497</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44586</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44511</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44615</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44613</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44593</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44523</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44824</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44504</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44609</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44525</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>44606</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44867</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44692</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44734</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44615</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44859</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44833</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44859</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44739</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44515</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>44735</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>44854</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>44728</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>44538</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>44635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>44735</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>44592</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>44648</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44706</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>44706</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>45744</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>44804</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>45804</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>44855</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>44601</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>45618</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>45426</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44743</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>45329</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>45267</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>45040</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>44545</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45217</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>44938</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>44948</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>45512</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>44901</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45105</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>44657</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>45385</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>45359</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44739</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>45901</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45904</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45356</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45904</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45895</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45086</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45436</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>45670</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>44943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>45896</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>45245</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>45903</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>44935</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>45916</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>45155</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>45915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>44914</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45678</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45917</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>46163</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>46163</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45917</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45596</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>46167</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>45005</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44893</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>45196</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44687</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45860</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>45926</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>45698</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>46169</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45136</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45926</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45128</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>46169</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>46170</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45929</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>45929</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>46171</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>46170</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>46170</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45146</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44978</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45288</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>45547</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>45478</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45359</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>45933</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>45936</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45236</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>44995</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>46175</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45407</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>46175</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45217</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>45890</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45259</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45673</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45706</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45384</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>44754</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>45210</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>46177</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45128</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45407</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>44901</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>44901</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45692</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45159</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45954</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45169</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44998</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>46185</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>46186</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45089</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45708</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45965</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>46188</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45965</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45965</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45254</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45831</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45336</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>45328</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45055</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45105</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>45635</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>46196</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45032</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>46196</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45978</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>45596</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45106</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>45978</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>45978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>45978</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>44620</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>45362</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>44911</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>45308</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>45544</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>45979</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>46203</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>44978</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>44994</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>45267</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>44839</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>46204</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45530</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>46204</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>45986</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>44998</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>46204</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>46204</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45986</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45264</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>46209</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>46206</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45358</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>44958</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45992</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45992</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>46212</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45462</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44881</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45320</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>45996</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>45043</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44812</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>45418</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45551</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>45113</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45385</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>45616</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45700</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45407</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>46013</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>46279</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45341</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45949</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>45418</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>46281</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>46281</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>46238</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45440</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>45790</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>45456</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>46286</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>46286</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>46286</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45705</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>46241</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>46241</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45363</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>44973</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>46286</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>46241</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>46241</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>46241</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>46241</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>46286</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>46286</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>46037</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45544</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45436</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>46288</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45798</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45015</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>45418</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45391</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>46244</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45518</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>46288</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>44957</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>46287</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>46244</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>45362</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45800</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>44601</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>46050</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>46052</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>46051</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>45782</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>44816</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>45476</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44504</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>46290</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45342</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>46058</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>46246</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45811</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45811</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>45811</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45811</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>46293</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>46063</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>46064</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>46293</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45384</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>46296</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45342</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45824</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45821</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>46079</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45825</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>45827</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>46252</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>46081</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>46084</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>46084</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45831</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45769</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>45834</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>46087</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>45834</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>46297</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>45833</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45838</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45838</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>45989</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>45544</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>46094</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>46098</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>46098</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>45841</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>46300</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45012</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45847</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45852</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>46302</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>46259</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>44495</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45547</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45628</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45593</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>46303</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>46303</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44873</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>45868</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>46304</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>45467</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>46303</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>46303</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>46120</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45874</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>46122</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>46122</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>46092</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>45414</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>46122</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>46122</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45359</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45875</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>46129</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>46129</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45305</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>46132</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>46129</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>46132</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45518</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>45436</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45187</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>45460</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>45113</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44656</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>45471</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>45574</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>45300</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45362</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44938</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>45874</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>45856</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>45884</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>46136</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>46309</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>45189</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>45818</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>45838</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>45666</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>45909</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>45946</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>45349</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>44951</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45447</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45544</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32106,7 +32106,7 @@
         <v>45548</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32179,7 +32179,7 @@
         <v>45524</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45390</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>46058</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>45385</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32471,7 +32471,7 @@
         <v>45359</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32544,7 +32544,7 @@
         <v>45359</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32617,7 +32617,7 @@
         <v>46314</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32690,7 +32690,7 @@
         <v>46314</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>45840</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>45546</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         <v>46139</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>45988</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>45858</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>46269</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>45407</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>44838</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>46314</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>46272</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>46316</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>45565</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45834</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>46273</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>46316</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33858,7 +33858,7 @@
         <v>46316</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>46316</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>46273</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>46273</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34150,7 +34150,7 @@
         <v>44600</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>44972</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>45827</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>45338</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>46317</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>46317</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45229</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>46317</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>46142</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>46274</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>46317</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>46317</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>46274</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>45259</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35187,7 +35187,7 @@
         <v>45218</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35260,7 +35260,7 @@
         <v>44783</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>46084</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45608</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35479,7 +35479,7 @@
         <v>45068</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>45712</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35625,7 +35625,7 @@
         <v>44735</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>45959</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45854</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45426</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>45090</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45198</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36063,7 +36063,7 @@
         <v>45075</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>44991</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>45079</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>44735</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>44805</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>45166</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45166</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45385</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>44747</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45614</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>45614</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45135</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44783</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45163</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45673</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45673</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45664</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>45635</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45722</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>45005</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37523,7 +37523,7 @@
         <v>45629</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44820</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37669,7 +37669,7 @@
         <v>45740</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>45644</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>45113</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45476</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45763</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45092</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45267</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>45247</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>44805</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>45771</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45524</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45532</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45247</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45103</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45076</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45538</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>44868</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38910,7 +38910,7 @@
         <v>44749</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>44880</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45719</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45128</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45337</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39275,7 +39275,7 @@
         <v>45555</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45078</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>45296</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>45744</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>44935</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45726</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>45436</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45436</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>44816</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45015</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>45110</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>44907</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>45114</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45015</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45337</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>45519</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>44966</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>44925</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44601</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45463</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45540</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>45482</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>45000</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>45563</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>45180</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>45771</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>45771</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>45632</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>45418</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45418</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>45614</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45642</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>45161</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>45342</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45517</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45608</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45699</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45613</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>45328</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>45009</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>44998</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>45632</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45608</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45447</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45210</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45114</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>44569</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>44606</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>45733</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42862,7 +42862,7 @@
         <v>45218</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45471</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45471</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>45608</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45338</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43227,7 +43227,7 @@
         <v>45338</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43300,7 +43300,7 @@
         <v>45345</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45608</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>44523</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>44581</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45608</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>45182</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45366</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>45680</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43884,7 +43884,7 @@
         <v>45728</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45095</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>45400</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44103,7 +44103,7 @@
         <v>45653</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45173</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>45155</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45398</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>44743</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>44743</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45153</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45153</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         <v>45231</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>45288</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>45308</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44906,7 +44906,7 @@
         <v>45149</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45166</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>45135</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45217</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45198,7 +45198,7 @@
         <v>45336</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>45349</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45362</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45330</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>44670</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>45217</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45462</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>45264</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45272</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45166</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45740</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>45136</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45216</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>44895</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46225,7 +46225,7 @@
         <v>45595</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>45338</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>44970</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45180</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45302</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>44985</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>45532</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45324</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46809,7 +46809,7 @@
         <v>44635</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44991</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>44935</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>45336</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45436</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>44675</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>44675</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>44643</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>44743</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>45350</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>44903</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45111</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45532</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>45481</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>44497</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45532</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47977,7 +47977,7 @@
         <v>45267</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48050,7 +48050,7 @@
         <v>45435</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45709</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>45694</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>45720</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45694</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48415,7 +48415,7 @@
         <v>45701</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45714</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48561,7 +48561,7 @@
         <v>45694</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48634,7 +48634,7 @@
         <v>45814</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>45972</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>45971</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         <v>46040</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>46056</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>46071</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>46099</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>46191</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>46251</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49291,7 +49291,7 @@
         <v>46296</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49364,7 +49364,7 @@
         <v>46296</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>46251</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49510,7 +49510,7 @@
         <v>46304</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>46304</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -601,7 +601,7 @@
         <v>46041</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>44823</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45328</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>45756</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45730</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>45730</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46105</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45637</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45610</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45559</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45166</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>46297</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>46274</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>45041</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45587</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>45425</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44592</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44535</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45951</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45670</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>46241</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>46261</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>45763</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>45359</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>45638</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>45342</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45478</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>44512</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44643</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>46280</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44530</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>44819</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>44810</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>45446</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>45043</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>45106</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45112</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45373</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45378</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45996</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>46241</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>45573</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>45971</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>44853</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44798</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>45187</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45547</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44959</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>45210</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45198</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>46269</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>44805</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>44768</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>44805</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44810</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>44512</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>44597</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>44613</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44515</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44798</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44511</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44615</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44497</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44586</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44511</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44615</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44613</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44593</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44523</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44824</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44504</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44609</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44525</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>44606</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44867</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44692</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44734</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44615</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44859</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44833</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44859</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44739</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44515</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>44735</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>44854</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>44728</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>44538</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>44635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>44735</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>44592</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>44648</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44706</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>44706</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>45744</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>44804</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>45804</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>44855</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>44601</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>45618</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>45426</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44743</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>45329</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>45267</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>45040</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>44783</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>44545</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45217</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>44938</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>44948</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>45512</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>44901</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45105</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>44657</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>45385</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>45359</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44739</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>45901</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45904</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45356</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45904</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45895</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45086</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45436</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>45670</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>44943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>45896</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>45245</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>45903</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>44935</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>45916</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>45155</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>45915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>44914</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45678</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45917</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>46163</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>46163</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45917</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45596</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>46167</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>45005</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>44893</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>45196</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44687</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45860</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>45926</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>45698</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>46169</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45136</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45926</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45128</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>46169</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>46170</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45929</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>45929</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>46171</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>46170</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>46170</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45146</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44978</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45288</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>45547</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>45478</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45359</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>45933</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>45936</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45236</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>44995</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>46175</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45407</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>46175</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45217</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>45890</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45259</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45673</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45706</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45384</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>44754</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>45210</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>46177</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45128</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45407</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>44901</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>44901</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45692</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45159</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45954</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45169</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44998</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>46185</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>46186</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45089</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45708</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45965</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>46188</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45965</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45965</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45254</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45831</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45336</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>45328</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45055</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45105</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>45635</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>46196</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45032</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>46196</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45978</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>45596</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45106</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>45978</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>45978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>45978</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>44620</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>45362</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>44911</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>45308</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>45544</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>45979</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>46203</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>44978</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>44994</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>45267</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>44839</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>46204</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45530</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>46204</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>45986</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>44998</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>46204</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>46204</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45986</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45264</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>46209</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>46206</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45358</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>44958</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45992</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45992</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>46212</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45462</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44881</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45320</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>45996</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>45043</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44812</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>45418</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45551</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>45113</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45385</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>45616</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45700</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45407</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>46013</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>46279</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45341</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45949</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>45418</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>46281</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>46281</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>46238</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45440</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>45790</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>45456</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>46286</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>46286</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>46286</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45705</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>46241</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>46241</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45363</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>44973</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>46286</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>46241</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>46241</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>46241</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>46241</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>46286</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>46286</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>46037</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45544</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45436</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>46288</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45798</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45015</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>45418</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45391</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>46244</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45518</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>46288</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>44957</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>46287</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>46244</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>45362</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45800</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>44601</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>46050</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>46052</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>46051</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>45782</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>44816</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>45476</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44504</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>46290</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45342</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>46058</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>46246</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45811</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45811</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>45811</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45811</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>46293</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>46063</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>46064</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>46293</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45384</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>46296</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45342</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45824</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45821</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>46079</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45825</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>45827</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>46252</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>46081</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>46084</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>46084</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45831</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45769</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>45834</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>46087</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>45834</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>46297</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>45833</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45838</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45838</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>45989</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>45544</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>46094</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>46098</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>46098</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>45841</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>46300</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45012</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45847</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45852</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>46302</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>46259</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>44495</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45547</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45628</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45593</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>46303</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>46303</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44873</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>45868</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>46304</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>45467</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>46303</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>46303</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>46120</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45874</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>46122</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>46122</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>46092</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>45414</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>46122</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>46122</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45359</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45875</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>46129</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>46129</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45305</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>46132</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>46129</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>46132</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45518</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>45436</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45187</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>45460</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>45113</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44656</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>45471</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>45574</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>45300</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45362</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44938</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>45874</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>45856</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>45884</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>46136</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>46309</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>45189</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>45818</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>45838</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>45666</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>45909</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>45946</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>45349</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>44951</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45447</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45544</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32106,7 +32106,7 @@
         <v>45548</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32179,7 +32179,7 @@
         <v>45524</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32252,7 +32252,7 @@
         <v>45390</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>46058</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>45385</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32471,7 +32471,7 @@
         <v>45359</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32544,7 +32544,7 @@
         <v>45359</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32617,7 +32617,7 @@
         <v>46314</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32690,7 +32690,7 @@
         <v>46314</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>45840</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>45546</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         <v>46139</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>45988</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>45858</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>46269</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>45407</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>44838</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>46314</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>46272</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>46316</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>45565</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45834</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>46273</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>46316</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33858,7 +33858,7 @@
         <v>46316</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>46316</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>46273</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>46273</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34150,7 +34150,7 @@
         <v>44600</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>44972</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>45827</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>45338</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>46317</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>46317</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45229</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>46317</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>46142</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>46274</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>46317</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>46317</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>46274</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>45259</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35187,7 +35187,7 @@
         <v>45218</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35260,7 +35260,7 @@
         <v>44783</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>46084</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45608</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35479,7 +35479,7 @@
         <v>45068</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>45712</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35625,7 +35625,7 @@
         <v>44735</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35698,7 +35698,7 @@
         <v>45959</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45854</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45426</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>45090</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>45198</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36063,7 +36063,7 @@
         <v>45075</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>44991</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>45079</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>44735</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>44805</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>45166</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45166</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45385</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>44747</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45614</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>45614</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36866,7 +36866,7 @@
         <v>45135</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44783</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45163</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45673</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45673</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45664</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>45635</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45722</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>45005</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37523,7 +37523,7 @@
         <v>45629</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44820</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37669,7 +37669,7 @@
         <v>45740</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>45644</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>45113</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45476</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45763</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45092</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45267</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>45247</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>44805</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>45771</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45524</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45532</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45247</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45103</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45076</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45538</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>44868</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38910,7 +38910,7 @@
         <v>44749</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>44880</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45719</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45128</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45337</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39275,7 +39275,7 @@
         <v>45555</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45078</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>45296</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>45744</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>44935</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45726</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>45436</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45436</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>44816</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45015</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>45110</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>44907</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>45114</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45015</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45337</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>45519</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>44966</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>44925</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44601</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45463</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45540</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>45482</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>45000</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>45563</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>45180</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>45771</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>45771</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>45632</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>45418</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45418</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>45614</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45642</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>45161</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>45342</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45517</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45608</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45699</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45613</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>45328</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>45009</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>44998</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>45632</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45608</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45447</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45210</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45114</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>44569</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>44606</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>45733</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42862,7 +42862,7 @@
         <v>45218</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45471</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45471</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>45608</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45338</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43227,7 +43227,7 @@
         <v>45338</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43300,7 +43300,7 @@
         <v>45345</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45608</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>44523</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>44581</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45608</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>45182</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45366</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>45680</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43884,7 +43884,7 @@
         <v>45728</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45095</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>45400</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44103,7 +44103,7 @@
         <v>45653</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45173</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>45155</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45398</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>44743</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>44743</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45153</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45153</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         <v>45231</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>45288</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>45308</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44906,7 +44906,7 @@
         <v>45149</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45166</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>45135</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45125,7 +45125,7 @@
         <v>45217</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45198,7 +45198,7 @@
         <v>45336</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>45349</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45344,7 +45344,7 @@
         <v>45362</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>45330</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>44670</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>45217</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45462</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>45264</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45272</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45166</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45740</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>45136</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45216</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>44895</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46225,7 +46225,7 @@
         <v>45595</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>45338</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>44970</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>45180</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45302</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>44985</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>45532</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45324</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46809,7 +46809,7 @@
         <v>44635</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44991</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>44935</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>45336</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45436</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>44675</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>44675</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>44643</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>44743</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>45350</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>44903</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45111</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45532</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>45481</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>44497</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45532</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47977,7 +47977,7 @@
         <v>45267</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48050,7 +48050,7 @@
         <v>45435</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45709</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>45694</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>45720</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45694</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48415,7 +48415,7 @@
         <v>45701</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45714</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48561,7 +48561,7 @@
         <v>45694</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48634,7 +48634,7 @@
         <v>45814</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>45972</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>45971</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         <v>46040</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>46056</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>46071</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>46099</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>46191</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>46251</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49291,7 +49291,7 @@
         <v>46296</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49364,7 +49364,7 @@
         <v>46296</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>46251</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49510,7 +49510,7 @@
         <v>46304</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>46304</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
